--- a/artfynd/A 41346-2024 artfynd.xlsx
+++ b/artfynd/A 41346-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79051958</v>
+        <v>79051949</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397448.8950462503</v>
+        <v>397304</v>
       </c>
       <c r="R2" t="n">
-        <v>6705121.232982033</v>
+        <v>6705180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79051949</v>
+        <v>81088473</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Buberget/Busjön, Öster om Ljusnan, Vrm</t>
+          <t>SO om Fagertjärnåsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397303.7855391982</v>
+        <v>397468</v>
       </c>
       <c r="R3" t="n">
-        <v>6705180.114792042</v>
+        <v>6705121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +845,7 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
         <is>
           <t>2019-07-18</t>
         </is>
@@ -897,27 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79051979</v>
+        <v>79051969</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397474.1253524006</v>
+        <v>397307</v>
       </c>
       <c r="R4" t="n">
-        <v>6705157.029673044</v>
+        <v>6705214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79051975</v>
+        <v>79051979</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397309.9532127198</v>
+        <v>397474</v>
       </c>
       <c r="R5" t="n">
-        <v>6705171.058671488</v>
+        <v>6705157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1044,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79051947</v>
+        <v>79051975</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397381.8857311616</v>
+        <v>397310</v>
       </c>
       <c r="R6" t="n">
-        <v>6705145.828719373</v>
+        <v>6705171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1146,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79051969</v>
+        <v>79051958</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397307.2197897402</v>
+        <v>397449</v>
       </c>
       <c r="R7" t="n">
-        <v>6705214.061413187</v>
+        <v>6705121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1248,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1377,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81088471</v>
+        <v>79051947</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,34 +1293,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SO om Fagertjärnåsen, Vrm</t>
+          <t>Buberget/Busjön, Öster om Ljusnan, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397440.150968498</v>
+        <v>397382</v>
       </c>
       <c r="R8" t="n">
-        <v>6705109.145701452</v>
+        <v>6705146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1350,14 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på rönn</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,27 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81088473</v>
+        <v>81088471</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397468.1677089693</v>
+        <v>397440</v>
       </c>
       <c r="R9" t="n">
-        <v>6705121.180343065</v>
+        <v>6705109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,19 +1452,14 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på rönn</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 41346-2024 artfynd.xlsx
+++ b/artfynd/A 41346-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81088473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051969</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051975</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051958</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051947</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,8 +1523,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81088471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>